--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,138 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E8" s="3">
         <v>32200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12500</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -836,8 +843,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,8 +896,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1023,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,8 +1076,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E17" s="3">
         <v>14300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1800</v>
       </c>
       <c r="K17" s="3">
         <v>1800</v>
       </c>
       <c r="L17" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="M17" s="3">
         <v>2100</v>
       </c>
       <c r="N17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>17900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,108 +1276,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>11700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>4000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,108 +1433,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E23" s="3">
         <v>11300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1400</v>
       </c>
       <c r="J24" s="3">
         <v>1400</v>
       </c>
       <c r="K24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>500</v>
       </c>
       <c r="O24" s="3">
         <v>500</v>
       </c>
       <c r="P24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>8800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>8800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1910,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E32" s="3">
         <v>6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>8800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>8800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2224,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E41" s="3">
         <v>21300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,44 +2275,47 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E42" s="3">
         <v>244600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>175600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>153200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>228700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>168200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>186000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>277600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>158800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>170200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>153200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,8 +2328,11 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2288,8 +2381,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,8 +2434,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2388,8 +2487,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2438,44 +2540,47 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="E47" s="3">
         <v>3800</v>
       </c>
       <c r="F47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G47" s="3">
         <v>4400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8900</v>
-      </c>
-      <c r="J47" s="3">
-        <v>9200</v>
       </c>
       <c r="K47" s="3">
         <v>9200</v>
       </c>
       <c r="L47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M47" s="3">
         <v>9000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,44 +2593,47 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E48" s="3">
         <v>27000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,44 +2646,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E49" s="3">
         <v>17900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>18200</v>
       </c>
       <c r="H49" s="3">
         <v>18200</v>
       </c>
       <c r="I49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J49" s="3">
         <v>18300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>18400</v>
       </c>
       <c r="K49" s="3">
         <v>18400</v>
       </c>
       <c r="L49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="M49" s="3">
         <v>18500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18600</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2699,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2738,8 +2858,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,44 +2911,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2296500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2277800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2135600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2045200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2052700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1902500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1798800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1782600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1559100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1514400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1459200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,8 +2964,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,25 +3008,26 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -2908,14 +3039,14 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,8 +3059,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2978,8 +3112,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3028,8 +3165,11 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3078,32 +3218,35 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E61" s="3">
         <v>86500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86300</v>
-      </c>
-      <c r="G61" s="3">
-        <v>47000</v>
       </c>
       <c r="H61" s="3">
         <v>47000</v>
       </c>
       <c r="I61" s="3">
+        <v>47000</v>
+      </c>
+      <c r="J61" s="3">
         <v>47200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3111,11 +3254,11 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>4500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3128,8 +3271,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,44 +3483,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2094600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2080600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1946000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1863500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1882400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1734500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1629600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1605400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1384800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1365500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1314600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3536,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,44 +3769,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E72" s="3">
         <v>88600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>80600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>73800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>42400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>39200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3822,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,44 +3981,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201900</v>
+      </c>
+      <c r="E76" s="3">
         <v>197300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>181700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>170300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>167900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>169200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>174200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>148900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>144600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3848,8 +4034,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>8800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4221,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4047,7 +4246,7 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -4062,19 +4261,22 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>500</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4537,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E89" s="3">
         <v>11300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-5900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4613,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4770,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-66300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-98700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-126200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-98100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-119200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-52800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-74500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4640,7 +4874,7 @@
         <v>-800</v>
       </c>
       <c r="K96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="L96" s="3">
         <v>-700</v>
@@ -4649,7 +4883,7 @@
         <v>-700</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5056,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E100" s="3">
         <v>134100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>81700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>142600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>218400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>51900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>120900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>74700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E102" s="3">
         <v>73100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-77600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>106100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-22600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-5700</v>
       </c>
-      <c r="R102" s="3" t="s">
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,145 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F8" s="3">
         <v>35200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>32200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>28700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>26700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>17800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>15900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>15200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>14700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>14200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>12800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>12100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>12500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -846,8 +859,14 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -899,8 +918,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,8 +1059,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1079,8 +1118,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1177,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1201,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F17" s="3">
         <v>15200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>14300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2800</v>
       </c>
       <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>20000</v>
+        <v>19600</v>
       </c>
       <c r="E18" s="3">
         <v>17900</v>
       </c>
       <c r="F18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>17900</v>
+      </c>
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>18900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>17800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>14000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>13400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>12900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>12100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>11600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>9400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,114 +1342,128 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11500</v>
+        <v>-9100</v>
       </c>
       <c r="E20" s="3">
         <v>-6600</v>
       </c>
       <c r="F20" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="H20" s="3">
         <v>-8400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-5800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-8900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-8300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-7900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-7100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-5500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F21" s="3">
         <v>8900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>11700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>10400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>13500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>9300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>7200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1436,114 +1515,132 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F23" s="3">
         <v>8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>11300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>6000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2300</v>
       </c>
       <c r="G24" s="3">
         <v>2500</v>
       </c>
       <c r="H24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1692,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F26" s="3">
         <v>6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>8800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>7700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F27" s="3">
         <v>6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>8800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>7700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>6700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1928,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,114 +2046,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11500</v>
+        <v>9100</v>
       </c>
       <c r="E32" s="3">
         <v>6600</v>
       </c>
       <c r="F32" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H32" s="3">
         <v>8400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>5800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>8900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>8300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>7900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>7100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>5500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F33" s="3">
         <v>6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>8800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>7700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>6700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2223,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F35" s="3">
         <v>6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>8800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>7700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>6700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,50 +2396,52 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F41" s="3">
         <v>31000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>15300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>22200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>22900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>19000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>18000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>17500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,50 +2451,56 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>230900</v>
+      </c>
+      <c r="F42" s="3">
         <v>185100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>244600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>175600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>153200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>228700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>168200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>186000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>277600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>158800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>170200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>153200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,8 +2510,14 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2384,8 +2569,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2437,8 +2628,14 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2490,8 +2687,14 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2543,50 +2746,56 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F47" s="3">
         <v>3700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>4400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>7000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>8900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>9200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>9200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>9000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>5000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2596,50 +2805,56 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F48" s="3">
         <v>26700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>27000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>27100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>27300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>28600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>28500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>28100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>24900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,50 +2864,56 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E49" s="3">
         <v>17800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="G49" s="3">
         <v>17900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>18000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>18100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>18200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>18200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>18300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>18400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>18400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>18500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>18600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,8 +2923,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,8 +3041,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2861,8 +3100,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,50 +3159,56 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2511000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2446700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2296500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2277800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2135600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2045200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2052700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1902500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1798800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1782600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1559100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1514400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1459200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2967,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,31 +3268,33 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3042,17 +3303,17 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,8 +3323,14 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3115,8 +3382,14 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3168,8 +3441,14 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3221,50 +3500,56 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>86700</v>
+      </c>
+      <c r="F61" s="3">
         <v>86600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>86500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>86400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>86300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>47000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>47000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>47200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>4500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3559,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3327,8 +3618,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,50 +3795,56 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2288100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2231700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2094600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2080600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1946000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1863500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1882400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1734500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1629600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1605400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1384800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1365500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1314600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,50 +4113,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>102500</v>
+      </c>
+      <c r="F72" s="3">
         <v>94400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>88600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>80600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>73800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>64000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>58000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>53600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>49900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>46600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>42400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>39200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3825,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,50 +4349,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>222900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F76" s="3">
         <v>201900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>197300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>189700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>181700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>170300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>167900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>169200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>177200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>174200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>148900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>144600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4037,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4467,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F81" s="3">
         <v>6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>8800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>7700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>6700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4617,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4249,10 +4646,10 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -4264,10 +4661,10 @@
         <v>500</v>
       </c>
       <c r="P83" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+        <v>500</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>600</v>
@@ -4275,8 +4672,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>600</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4967,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F89" s="3">
         <v>11200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>8900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>9500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>11800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>7700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>7100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>13100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>-5900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,16 +5053,18 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4632,43 +5073,49 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +5226,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-79200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-68700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-72300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-66300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-64200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-98700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-126200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-98100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-119200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-56400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-37000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-48100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-52800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-74500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5312,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4877,19 +5344,19 @@
         <v>-800</v>
       </c>
       <c r="L96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="M96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="N96" s="3">
         <v>-700</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4900,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5544,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>138100</v>
+      </c>
+      <c r="F100" s="3">
         <v>7800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>134100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>81700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-22800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>142600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>100000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>13100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>218400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>39000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>51900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>120900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>27500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>74700</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5165,57 +5662,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-49700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>73100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>24300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-77600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>55700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-18500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-75100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>106100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-10300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>17400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>85800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-22300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-5700</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,158 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E8" s="3">
         <v>38700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>36200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +872,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E17" s="3">
         <v>19100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1800</v>
       </c>
       <c r="N17" s="3">
         <v>1800</v>
       </c>
       <c r="O17" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="P17" s="3">
         <v>2100</v>
       </c>
       <c r="Q17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E18" s="3">
         <v>19600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1377,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E21" s="3">
         <v>10900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>4000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,8 +1561,11 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1530,117 +1573,123 @@
         <v>10500</v>
       </c>
       <c r="E23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F23" s="3">
         <v>11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1400</v>
       </c>
       <c r="M24" s="3">
         <v>1400</v>
       </c>
       <c r="N24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>500</v>
       </c>
       <c r="R24" s="3">
         <v>500</v>
       </c>
       <c r="S24" s="3">
+        <v>500</v>
+      </c>
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2700</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>9100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,53 +2484,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E41" s="3">
         <v>20500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>31000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,53 +2544,56 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E42" s="3">
         <v>216700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>230900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>185100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>244600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>175600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>153200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>228700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>168200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>186000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>277600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>158800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>170200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>153200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2516,8 +2606,11 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,8 +2730,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2693,8 +2792,11 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2752,53 +2854,56 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E47" s="3">
         <v>3600</v>
       </c>
       <c r="F47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G47" s="3">
         <v>3700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3800</v>
       </c>
       <c r="H47" s="3">
         <v>3800</v>
       </c>
       <c r="I47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J47" s="3">
         <v>4400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>9200</v>
       </c>
       <c r="N47" s="3">
         <v>9200</v>
       </c>
       <c r="O47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P47" s="3">
         <v>9000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,53 +2916,56 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E48" s="3">
         <v>26300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,53 +2978,56 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E49" s="3">
         <v>17700</v>
-      </c>
-      <c r="E49" s="3">
-        <v>17800</v>
       </c>
       <c r="F49" s="3">
         <v>17800</v>
       </c>
       <c r="G49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="H49" s="3">
         <v>17900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>18200</v>
       </c>
       <c r="K49" s="3">
         <v>18200</v>
       </c>
       <c r="L49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="M49" s="3">
         <v>18300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>18400</v>
       </c>
       <c r="N49" s="3">
         <v>18400</v>
       </c>
       <c r="O49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="P49" s="3">
         <v>18500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,53 +3288,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2572000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2511000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2446700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2296500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2277800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2135600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2045200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2052700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1902500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1798800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1782600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1559100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1514400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1459200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,34 +3400,35 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -3309,14 +3440,14 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3388,8 +3522,11 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3447,8 +3584,11 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3506,41 +3646,44 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E61" s="3">
         <v>86800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>86500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>86400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>86300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>47000</v>
       </c>
       <c r="K61" s="3">
         <v>47000</v>
       </c>
       <c r="L61" s="3">
+        <v>47000</v>
+      </c>
+      <c r="M61" s="3">
         <v>47200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3548,11 +3691,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>4500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3565,8 +3708,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,53 +3956,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2341400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2288100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2231700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2094600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2080600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1946000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1863500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1882400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1734500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1629600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1605400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1384800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1365500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1314600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,53 +4290,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E72" s="3">
         <v>109800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>102500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>94400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>88600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>80600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>73800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>64000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>58000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>42400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,53 +4538,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E76" s="3">
         <v>222900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>215000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>201900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>197300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>189700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>181700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>167900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>169200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>177200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>174200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4652,7 +4851,7 @@
         <v>400</v>
       </c>
       <c r="M83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
@@ -4667,19 +4866,22 @@
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>11400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>-6500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-79200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-111500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-72300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-66300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-98700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-126200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-98100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-119200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-56400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-48100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-52800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-74500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5350,7 +5584,7 @@
         <v>-800</v>
       </c>
       <c r="N96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="O96" s="3">
         <v>-700</v>
@@ -5359,7 +5593,7 @@
         <v>-700</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E100" s="3">
         <v>54300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>138100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>134100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>81700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>142600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>218400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>51900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>120900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>74700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-49700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>73100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-77600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>106100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>85800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-22300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-22600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-5700</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,165 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>41000</v>
+        <v>23400</v>
       </c>
       <c r="E8" s="3">
-        <v>38700</v>
+        <v>21900</v>
       </c>
       <c r="F8" s="3">
-        <v>36200</v>
+        <v>20900</v>
       </c>
       <c r="G8" s="3">
-        <v>35200</v>
+        <v>20900</v>
       </c>
       <c r="H8" s="3">
-        <v>32200</v>
+        <v>17100</v>
       </c>
       <c r="I8" s="3">
-        <v>28700</v>
+        <v>24700</v>
       </c>
       <c r="J8" s="3">
+        <v>20200</v>
+      </c>
+      <c r="K8" s="3">
         <v>26700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12500</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,31 +882,34 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>20200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,31 +1102,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-1600</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1147,31 +1167,34 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20500</v>
+        <v>11800</v>
       </c>
       <c r="E17" s="3">
-        <v>19100</v>
+        <v>11000</v>
       </c>
       <c r="F17" s="3">
-        <v>18300</v>
+        <v>10000</v>
       </c>
       <c r="G17" s="3">
-        <v>15200</v>
+        <v>11000</v>
       </c>
       <c r="H17" s="3">
-        <v>14300</v>
+        <v>8200</v>
       </c>
       <c r="I17" s="3">
-        <v>10300</v>
+        <v>13300</v>
       </c>
       <c r="J17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1800</v>
       </c>
       <c r="O17" s="3">
         <v>1800</v>
       </c>
       <c r="P17" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="Q17" s="3">
         <v>2100</v>
       </c>
       <c r="R17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>20500</v>
+        <v>11700</v>
       </c>
       <c r="E18" s="3">
-        <v>19600</v>
+        <v>10800</v>
       </c>
       <c r="F18" s="3">
-        <v>17900</v>
+        <v>10900</v>
       </c>
       <c r="G18" s="3">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H18" s="3">
-        <v>17900</v>
+        <v>8800</v>
       </c>
       <c r="I18" s="3">
-        <v>18400</v>
+        <v>11500</v>
       </c>
       <c r="J18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K18" s="3">
         <v>18900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,155 +1411,162 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-10000</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>-9100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>400</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="P20" s="3">
         <v>-6600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-11500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5500</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E21" s="3">
         <v>10800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10900</v>
       </c>
-      <c r="F21" s="3">
-        <v>11600</v>
-      </c>
       <c r="G21" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="3">
         <v>8900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>4000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1564,132 +1604,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>10500</v>
+        <v>9700</v>
       </c>
       <c r="E23" s="3">
         <v>10500</v>
       </c>
       <c r="F23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="G23" s="3">
         <v>11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1400</v>
       </c>
       <c r="N24" s="3">
         <v>1400</v>
       </c>
       <c r="O24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>500</v>
       </c>
       <c r="S24" s="3">
         <v>500</v>
       </c>
       <c r="T24" s="3">
+        <v>500</v>
+      </c>
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E26" s="3">
         <v>8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2700</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E27" s="3">
         <v>8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>10000</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>9100</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>8300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="P32" s="3">
         <v>6600</v>
       </c>
-      <c r="G32" s="3">
-        <v>11500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>8900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>8300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>8000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>7900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>6600</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5500</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E33" s="3">
         <v>8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E35" s="3">
         <v>8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2571,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>21600</v>
+        <v>277900</v>
       </c>
       <c r="E41" s="3">
-        <v>20500</v>
+        <v>238400</v>
       </c>
       <c r="F41" s="3">
-        <v>19700</v>
+        <v>237100</v>
       </c>
       <c r="G41" s="3">
-        <v>31000</v>
+        <v>250700</v>
       </c>
       <c r="H41" s="3">
-        <v>21300</v>
+        <v>216200</v>
       </c>
       <c r="I41" s="3">
-        <v>17200</v>
+        <v>265900</v>
       </c>
       <c r="J41" s="3">
+        <v>192800</v>
+      </c>
+      <c r="K41" s="3">
         <v>15300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>18000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,56 +2634,59 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>216800</v>
+        <v>6100</v>
       </c>
       <c r="E42" s="3">
-        <v>216700</v>
+        <v>7600</v>
       </c>
       <c r="F42" s="3">
-        <v>230900</v>
+        <v>7800</v>
       </c>
       <c r="G42" s="3">
-        <v>185100</v>
+        <v>7700</v>
       </c>
       <c r="H42" s="3">
-        <v>244600</v>
+        <v>9600</v>
       </c>
       <c r="I42" s="3">
-        <v>175600</v>
+        <v>8400</v>
       </c>
       <c r="J42" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K42" s="3">
         <v>153200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>228700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>168200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>186000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>277600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>158800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>170200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>153200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,31 +2699,34 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2671,8 +2764,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2689,13 +2785,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2733,31 +2829,34 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2795,31 +2894,34 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>294600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>257300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>255000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>238800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>286200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>212500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2857,56 +2959,59 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3700</v>
+        <v>224400</v>
       </c>
       <c r="E47" s="3">
-        <v>3600</v>
+        <v>211500</v>
       </c>
       <c r="F47" s="3">
-        <v>3600</v>
+        <v>204800</v>
       </c>
       <c r="G47" s="3">
-        <v>3700</v>
+        <v>207000</v>
       </c>
       <c r="H47" s="3">
-        <v>3800</v>
+        <v>197200</v>
       </c>
       <c r="I47" s="3">
-        <v>3800</v>
+        <v>189400</v>
       </c>
       <c r="J47" s="3">
+        <v>189900</v>
+      </c>
+      <c r="K47" s="3">
         <v>4400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>9200</v>
       </c>
       <c r="O47" s="3">
         <v>9200</v>
       </c>
       <c r="P47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>9000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2919,56 +3024,59 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E48" s="3">
         <v>26200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,56 +3089,59 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E49" s="3">
         <v>17600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>17800</v>
       </c>
       <c r="G49" s="3">
         <v>17800</v>
       </c>
       <c r="H49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I49" s="3">
         <v>17900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18100</v>
-      </c>
-      <c r="K49" s="3">
-        <v>18200</v>
       </c>
       <c r="L49" s="3">
         <v>18200</v>
       </c>
       <c r="M49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="N49" s="3">
         <v>18300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>18400</v>
       </c>
       <c r="O49" s="3">
         <v>18400</v>
       </c>
       <c r="P49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="Q49" s="3">
         <v>18500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18600</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,31 +3284,34 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>78700</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>69800</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>62200</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>62600</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3414,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2841400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2572000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2511000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2446700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2296500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2277800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2135600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2045200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2052700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1902500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1798800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1782600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1559100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1514400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1459200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,37 +3531,38 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2000</v>
+        <v>2420500</v>
       </c>
       <c r="E57" s="3">
-        <v>1800</v>
+        <v>2175700</v>
       </c>
       <c r="F57" s="3">
-        <v>1500</v>
+        <v>2109800</v>
       </c>
       <c r="G57" s="3">
-        <v>1300</v>
+        <v>2018200</v>
       </c>
       <c r="H57" s="3">
-        <v>1100</v>
+        <v>1916400</v>
       </c>
       <c r="I57" s="3">
-        <v>800</v>
+        <v>1923900</v>
       </c>
       <c r="J57" s="3">
+        <v>1789500</v>
+      </c>
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -3443,14 +3574,14 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,31 +3594,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>36100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>67800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>104900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>32300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3525,31 +3659,34 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3587,31 +3724,34 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>2458900</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>2235300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>2179400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>2124600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1975300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1958400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1822700</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3649,44 +3789,47 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E61" s="3">
         <v>86900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86800</v>
       </c>
-      <c r="F61" s="3">
-        <v>86700</v>
-      </c>
       <c r="G61" s="3">
-        <v>86600</v>
+        <v>87000</v>
       </c>
       <c r="H61" s="3">
-        <v>86500</v>
+        <v>98600</v>
       </c>
       <c r="I61" s="3">
-        <v>86400</v>
+        <v>106500</v>
       </c>
       <c r="J61" s="3">
+        <v>106400</v>
+      </c>
+      <c r="K61" s="3">
         <v>86300</v>
-      </c>
-      <c r="K61" s="3">
-        <v>47000</v>
       </c>
       <c r="L61" s="3">
         <v>47000</v>
       </c>
       <c r="M61" s="3">
+        <v>47000</v>
+      </c>
+      <c r="N61" s="3">
         <v>47200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3694,11 +3837,11 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>4500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,31 +3854,34 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>20100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>15700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,56 +4114,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2570100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2341400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2288100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2231700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2094600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2080600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1946000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1863500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1882400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1734500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1629600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1605400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1384800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1365500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1314600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4464,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E72" s="3">
         <v>117200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>109800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>102500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>94400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>88600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>80600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>73800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>64000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>58000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>49900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>42400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4724,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271400</v>
+      </c>
+      <c r="E76" s="3">
         <v>230600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>222900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>215000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>197300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>189700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>181700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>170300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>167900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>169200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>177200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>174200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>144600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E81" s="3">
         <v>8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,31 +5016,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -4854,7 +5053,7 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>500</v>
@@ -4869,19 +5068,22 @@
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E89" s="3">
         <v>7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
         <v>-5900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5496,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
         <v>-6500</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-79200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-66300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-98700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-126200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-98100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-119200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-56400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-48100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-52800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
         <v>-74500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5781,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="E96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="F96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="G96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="H96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="I96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="J96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="K96" s="3">
         <v>-800</v>
@@ -5587,7 +5821,7 @@
         <v>-800</v>
       </c>
       <c r="O96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="P96" s="3">
         <v>-700</v>
@@ -5596,7 +5830,7 @@
         <v>-700</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,93 +6039,99 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-84600</v>
+      </c>
+      <c r="E100" s="3">
         <v>55200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>54300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>138100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>134100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>81700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>142600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>218400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>51900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>120900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>74700</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-49700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>73100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-77600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-75100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>106100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-22300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-22600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>-5700</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,172 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>20900</v>
       </c>
       <c r="G8" s="3">
         <v>20900</v>
       </c>
       <c r="H8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I8" s="3">
         <v>17100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -885,35 +891,38 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>20900</v>
       </c>
       <c r="G10" s="3">
         <v>20900</v>
       </c>
       <c r="H10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I10" s="3">
         <v>17100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,25 +1121,28 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1600</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1131,8 +1150,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1170,16 +1189,19 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
@@ -1197,7 +1219,7 @@
         <v>400</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E17" s="3">
         <v>11800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
-        <v>11000</v>
-      </c>
       <c r="H17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I17" s="3">
         <v>8200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1900</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1800</v>
       </c>
       <c r="P17" s="3">
         <v>1800</v>
       </c>
       <c r="Q17" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="R17" s="3">
         <v>2100</v>
       </c>
       <c r="S17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E18" s="3">
         <v>11700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10900</v>
       </c>
-      <c r="G18" s="3">
-        <v>10000</v>
-      </c>
       <c r="H18" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I18" s="3">
         <v>8800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1430,120 +1463,126 @@
         <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5500</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E21" s="3">
         <v>11900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10900</v>
       </c>
-      <c r="G21" s="3">
-        <v>10000</v>
-      </c>
       <c r="H21" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I21" s="3">
         <v>8900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>4000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1568,8 +1607,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1607,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E23" s="3">
         <v>9700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>10500</v>
       </c>
       <c r="F23" s="3">
         <v>10500</v>
       </c>
       <c r="G23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H23" s="3">
         <v>11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1400</v>
       </c>
       <c r="O24" s="3">
         <v>1400</v>
       </c>
       <c r="P24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1800</v>
-      </c>
-      <c r="S24" s="3">
-        <v>500</v>
       </c>
       <c r="T24" s="3">
         <v>500</v>
       </c>
       <c r="U24" s="3">
+        <v>500</v>
+      </c>
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E26" s="3">
         <v>7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2700</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E27" s="3">
         <v>7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2210,120 +2279,126 @@
         <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5500</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E33" s="3">
         <v>7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2700</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E35" s="3">
         <v>7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2700</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,59 +2657,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E41" s="3">
         <v>277900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>238400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>237100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>250700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>216200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>265900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>192800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17500</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,59 +2723,62 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E42" s="3">
         <v>6100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>153200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>228700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>168200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>186000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>277600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>158800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>170200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>153200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,8 +2791,11 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2728,8 +2820,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2767,13 +2859,16 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
@@ -2785,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>2900</v>
@@ -2794,7 +2889,7 @@
         <v>2900</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2832,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2841,26 +2939,26 @@
         <v>10100</v>
       </c>
       <c r="E45" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F45" s="3">
         <v>9700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2897,35 +2995,38 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E46" s="3">
         <v>294600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>257300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>255000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>267500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>238800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>286200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>212500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2962,59 +3063,62 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223200</v>
+      </c>
+      <c r="E47" s="3">
         <v>224400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>211500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>204800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>207000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>197200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>189400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>189900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8900</v>
-      </c>
-      <c r="O47" s="3">
-        <v>9200</v>
       </c>
       <c r="P47" s="3">
         <v>9200</v>
       </c>
       <c r="Q47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="R47" s="3">
         <v>9000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,59 +3131,62 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E48" s="3">
         <v>32300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26300</v>
       </c>
-      <c r="G48" s="3">
-        <v>26400</v>
-      </c>
       <c r="H48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I48" s="3">
         <v>26700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,59 +3199,62 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E49" s="3">
         <v>40300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>17800</v>
       </c>
       <c r="H49" s="3">
         <v>17800</v>
       </c>
       <c r="I49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J49" s="3">
         <v>17900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>18200</v>
       </c>
       <c r="M49" s="3">
         <v>18200</v>
       </c>
       <c r="N49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="O49" s="3">
         <v>18300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>18400</v>
       </c>
       <c r="P49" s="3">
         <v>18400</v>
       </c>
       <c r="Q49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="R49" s="3">
         <v>18500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18600</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,35 +3403,38 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E52" s="3">
         <v>78700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>69800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67300</v>
       </c>
-      <c r="G52" s="3">
-        <v>54400</v>
-      </c>
       <c r="H52" s="3">
+        <v>53800</v>
+      </c>
+      <c r="I52" s="3">
         <v>64000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62600</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,59 +3539,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2848300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2841400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2572000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2511000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2446700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2296500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2277800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2135600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2045200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2052700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1902500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1798800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1782600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1559100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1514400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1459200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,40 +3661,41 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2411300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2420500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2175700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2109800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2018200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1916400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1923900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1789500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -3577,14 +3707,14 @@
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,35 +3727,38 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E58" s="3">
         <v>36100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>57600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>67800</v>
       </c>
-      <c r="G58" s="3">
-        <v>104900</v>
-      </c>
       <c r="H58" s="3">
+        <v>104700</v>
+      </c>
+      <c r="I58" s="3">
         <v>57600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3662,8 +3795,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3688,8 +3824,8 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3727,35 +3863,38 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2460200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2458900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2235300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2179400</v>
       </c>
-      <c r="G60" s="3">
-        <v>2124600</v>
-      </c>
       <c r="H60" s="3">
+        <v>2124400</v>
+      </c>
+      <c r="I60" s="3">
         <v>1975300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1958400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1822700</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3792,47 +3931,50 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E61" s="3">
         <v>91100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86800</v>
       </c>
-      <c r="G61" s="3">
-        <v>87000</v>
-      </c>
       <c r="H61" s="3">
+        <v>87200</v>
+      </c>
+      <c r="I61" s="3">
         <v>98600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>106500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>106400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>86300</v>
-      </c>
-      <c r="L61" s="3">
-        <v>47000</v>
       </c>
       <c r="M61" s="3">
         <v>47000</v>
       </c>
       <c r="N61" s="3">
+        <v>47000</v>
+      </c>
+      <c r="O61" s="3">
         <v>47200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3840,11 +3982,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>4500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3857,35 +3999,38 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E62" s="3">
         <v>20100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16900</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,59 +4271,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2568400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2570100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2341400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2288100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2231700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2094600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2080600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1946000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1863500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1882400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1734500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1629600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1605400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1384800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1365500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1314600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,59 +4637,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>134100</v>
+      </c>
+      <c r="E72" s="3">
         <v>123800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>117200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>109800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>102500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>94400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>88600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>80600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>73800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>64000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>58000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>42400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>39200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,59 +4909,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>279900</v>
+      </c>
+      <c r="E76" s="3">
         <v>271400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>230600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>222900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>215000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>201900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>197300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>189700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>181700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>170300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>167900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>169200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>177200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>174200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>148900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>144600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E81" s="3">
         <v>7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2700</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5044,7 +5242,7 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -5056,7 +5254,7 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
@@ -5071,19 +5269,22 @@
         <v>500</v>
       </c>
       <c r="T83" s="3">
+        <v>500</v>
+      </c>
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3">
         <v>-5900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
         <v>-6500</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E94" s="3">
         <v>114200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-61200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-79200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-72300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-66300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-98700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-126200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-98100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-119200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-48100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-52800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
         <v>-74500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,13 +6014,14 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E96" s="3">
         <v>800</v>
@@ -5809,7 +6042,7 @@
         <v>800</v>
       </c>
       <c r="K96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="L96" s="3">
         <v>-800</v>
@@ -5824,7 +6057,7 @@
         <v>-800</v>
       </c>
       <c r="P96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="Q96" s="3">
         <v>-700</v>
@@ -5833,7 +6066,7 @@
         <v>-700</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-84600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>55200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>54300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>138100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>134100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>81700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>142600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>218400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>51900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>120900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>74700</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,8 +6381,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>39500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-49700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>73100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-77600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>55700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-75100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>106100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>85800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-22300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-22600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>-5700</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E8" s="3">
         <v>28000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>20900</v>
       </c>
       <c r="H8" s="3">
         <v>20900</v>
       </c>
       <c r="I8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J8" s="3">
         <v>17100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,38 +901,41 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E10" s="3">
         <v>28000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>20900</v>
       </c>
       <c r="H10" s="3">
         <v>20900</v>
       </c>
       <c r="I10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J10" s="3">
         <v>17100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,37 +1141,40 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1201,10 +1224,10 @@
         <v>700</v>
       </c>
       <c r="E15" s="3">
+        <v>700</v>
+      </c>
+      <c r="F15" s="3">
         <v>600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
@@ -1222,7 +1245,7 @@
         <v>400</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E17" s="3">
         <v>12600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1800</v>
       </c>
       <c r="Q17" s="3">
         <v>1800</v>
       </c>
       <c r="R17" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="S17" s="3">
         <v>2100</v>
       </c>
       <c r="T17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E18" s="3">
         <v>15300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1466,123 +1500,129 @@
         <v>400</v>
       </c>
       <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5500</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E21" s="3">
         <v>15600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>4000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1610,8 +1650,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E23" s="3">
         <v>14900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>10500</v>
       </c>
       <c r="G23" s="3">
         <v>10500</v>
       </c>
       <c r="H23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I23" s="3">
         <v>11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>3700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1400</v>
       </c>
       <c r="P24" s="3">
         <v>1400</v>
       </c>
       <c r="Q24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>500</v>
       </c>
       <c r="U24" s="3">
         <v>500</v>
       </c>
       <c r="V24" s="3">
+        <v>500</v>
+      </c>
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E26" s="3">
         <v>11200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2700</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E27" s="3">
         <v>11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2282,123 +2352,129 @@
         <v>-400</v>
       </c>
       <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5500</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E33" s="3">
         <v>11200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2700</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="3">
         <v>11200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2700</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,62 +2744,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229400</v>
+      </c>
+      <c r="E41" s="3">
         <v>260200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>277900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>238400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>237100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>250700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>216200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>192800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,62 +2813,65 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E42" s="3">
         <v>6400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>153200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>228700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>168200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>186000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>277600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>158800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>170200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>153200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,8 +2884,11 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2823,8 +2916,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2862,16 +2955,19 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
@@ -2883,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
         <v>2900</v>
@@ -2892,7 +2988,7 @@
         <v>2900</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2930,38 +3026,41 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="E45" s="3">
         <v>10100</v>
       </c>
       <c r="F45" s="3">
+        <v>10100</v>
+      </c>
+      <c r="G45" s="3">
         <v>9700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2998,38 +3097,41 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>246700</v>
+      </c>
+      <c r="E46" s="3">
         <v>277200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>294600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>257300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>255000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>267500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>238800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>286200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>212500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3066,62 +3168,65 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E47" s="3">
         <v>223200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>224400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>211500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>204800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>207000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>197200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>189400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>189900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8900</v>
-      </c>
-      <c r="P47" s="3">
-        <v>9200</v>
       </c>
       <c r="Q47" s="3">
         <v>9200</v>
       </c>
       <c r="R47" s="3">
+        <v>9200</v>
+      </c>
+      <c r="S47" s="3">
         <v>9000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3134,62 +3239,65 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E48" s="3">
         <v>33000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,62 +3310,65 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E49" s="3">
         <v>42100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17700</v>
-      </c>
-      <c r="H49" s="3">
-        <v>17800</v>
       </c>
       <c r="I49" s="3">
         <v>17800</v>
       </c>
       <c r="J49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K49" s="3">
         <v>17900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18100</v>
-      </c>
-      <c r="M49" s="3">
-        <v>18200</v>
       </c>
       <c r="N49" s="3">
         <v>18200</v>
       </c>
       <c r="O49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="P49" s="3">
         <v>18300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>18400</v>
       </c>
       <c r="Q49" s="3">
         <v>18400</v>
       </c>
       <c r="R49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="S49" s="3">
         <v>18500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,38 +3523,41 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E52" s="3">
         <v>62700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>78700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>69800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>53800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>64000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62600</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,62 +3665,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2851100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2848300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2841400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2572000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2511000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2446700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2296500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2277800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2135600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2045200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2052700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1902500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1798800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1782600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1559100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1514400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1459200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,43 +3792,44 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2425600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2411300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2420500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2175700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2109800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2018200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1916400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1923900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1789500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -3710,14 +3841,14 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,38 +3861,41 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E58" s="3">
         <v>46700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>57600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>104700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>57600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3798,8 +3932,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3827,8 +3964,8 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -3866,38 +4003,41 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2452900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2460200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2458900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2235300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2179400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2124400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1975300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1958400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1822700</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3934,50 +4074,53 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E61" s="3">
         <v>91900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>91100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>86800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>98600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>106500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>106400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>86300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>47000</v>
       </c>
       <c r="N61" s="3">
         <v>47000</v>
       </c>
       <c r="O61" s="3">
+        <v>47000</v>
+      </c>
+      <c r="P61" s="3">
         <v>47200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3985,11 +4128,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>4500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4002,38 +4145,41 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E62" s="3">
         <v>9100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16900</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,62 +4429,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2561000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2568400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2570100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2341400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2288100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2231700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2094600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2080600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1946000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1863500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1882400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1734500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1629600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1605400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1384800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1365500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1314600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,62 +4811,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E72" s="3">
         <v>134100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>123800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>117200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>109800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>102500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>94400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>88600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>80600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>73800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>64000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>58000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>49900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>39200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,62 +5095,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>290200</v>
+      </c>
+      <c r="E76" s="3">
         <v>279900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>230600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>222900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>215000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>201900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>197300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>189700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>181700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>170300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>167900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>169200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>177200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>174200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>144600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E81" s="3">
         <v>11200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2700</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5245,7 +5444,7 @@
         <v>300</v>
       </c>
       <c r="L83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -5257,7 +5456,7 @@
         <v>400</v>
       </c>
       <c r="P83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
@@ -5272,19 +5471,22 @@
         <v>500</v>
       </c>
       <c r="U83" s="3">
+        <v>500</v>
+      </c>
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E89" s="3">
         <v>10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>-5900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
         <v>-6500</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>114200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-79200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-111500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-68700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-72300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-66300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-98700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-126200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-98100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-119200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-56400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-48100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-52800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27400</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
         <v>-74500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6024,7 +6258,7 @@
         <v>900</v>
       </c>
       <c r="E96" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F96" s="3">
         <v>800</v>
@@ -6045,7 +6279,7 @@
         <v>800</v>
       </c>
       <c r="L96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="M96" s="3">
         <v>-800</v>
@@ -6060,7 +6294,7 @@
         <v>-800</v>
       </c>
       <c r="Q96" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="R96" s="3">
         <v>-700</v>
@@ -6069,7 +6303,7 @@
         <v>-700</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-84600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>55200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>54300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>138100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>134100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>81700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>142600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>218400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>39000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>51900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>120900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>74700</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6384,8 +6633,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>73100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-77600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-75100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>106100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>85800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-22300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-22600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>-5700</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
